--- a/salidas/empresas/NOW.xlsx
+++ b/salidas/empresas/NOW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B4" t="n">
@@ -545,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B5" t="n">
@@ -570,7 +582,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B6" t="n">
@@ -595,7 +607,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B7" t="n">
@@ -620,7 +632,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B8" t="n">
@@ -645,7 +657,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B9" t="n">
@@ -670,7 +682,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B10" t="n">
@@ -695,7 +707,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B11" t="n">
@@ -720,7 +732,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B12" t="n">
@@ -745,7 +757,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B13" t="n">
@@ -770,7 +782,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B14" t="n">
@@ -795,7 +807,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B15" t="n">
@@ -820,7 +832,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B16" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B17" t="n">
@@ -870,7 +882,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B18" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B19" t="n">
@@ -920,7 +932,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B20" t="n">
@@ -945,7 +957,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B21" t="n">
@@ -970,7 +982,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B22" t="n">
@@ -997,7 +1009,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B23" t="n">
@@ -1024,7 +1036,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B24" t="n">
@@ -1051,7 +1063,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B25" t="n">
@@ -1078,7 +1090,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B26" t="n">
@@ -1105,7 +1117,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B27" t="n">
@@ -1132,7 +1144,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B28" t="n">
@@ -1159,7 +1171,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B29" t="n">
@@ -1186,7 +1198,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B30" t="n">
@@ -1213,7 +1225,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B31" t="n">
@@ -1240,7 +1252,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B32" t="n">
@@ -1267,7 +1279,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B33" t="n">
@@ -1294,7 +1306,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B34" t="n">
@@ -1321,7 +1333,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B35" t="n">
@@ -1348,7 +1360,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B36" t="n">
@@ -1375,7 +1387,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B37" t="n">
@@ -1402,7 +1414,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B38" t="n">
@@ -1429,7 +1441,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B39" t="n">
@@ -1456,7 +1468,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B40" t="n">
@@ -1483,7 +1495,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B41" t="n">
@@ -1510,7 +1522,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B42" t="n">
@@ -1537,7 +1549,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B43" t="n">
@@ -1564,7 +1576,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B44" t="n">
@@ -1591,7 +1603,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B45" t="n">
@@ -1618,7 +1630,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B46" t="n">
@@ -1645,7 +1657,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B47" t="n">
@@ -1672,7 +1684,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B48" t="n">
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B49" t="n">
@@ -1726,7 +1738,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B50" t="n">
@@ -1753,7 +1765,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B51" t="n">
@@ -1780,7 +1792,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B52" t="n">
@@ -1807,7 +1819,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B53" t="n">
@@ -1834,7 +1846,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B54" t="n">
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B55" t="n">
@@ -1888,7 +1900,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B56" t="n">
@@ -1915,7 +1927,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B57" t="n">
@@ -1942,7 +1954,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B58" t="n">
@@ -1969,7 +1981,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B59" t="n">
@@ -1996,7 +2008,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B60" t="n">
@@ -2023,7 +2035,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B61" t="n">
@@ -2050,7 +2062,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B62" t="n">
@@ -2077,7 +2089,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B63" t="n">
@@ -2104,7 +2116,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B64" t="n">
@@ -2131,7 +2143,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B65" t="n">
@@ -2158,7 +2170,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B66" t="n">
@@ -2183,7 +2195,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B67" t="n">
@@ -2208,7 +2220,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B68" t="n">
@@ -2233,7 +2245,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B69" t="n">
@@ -2258,7 +2270,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B70" t="n">
@@ -2283,7 +2295,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B71" t="n">
@@ -2308,7 +2320,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B72" t="n">
@@ -2333,7 +2345,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B73" t="n">
@@ -2360,7 +2372,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B74" t="n">
@@ -2387,7 +2399,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B75" t="n">
@@ -2414,7 +2426,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B76" t="n">
@@ -2441,7 +2453,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B77" t="n">
@@ -2468,7 +2480,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B78" t="n">
@@ -2495,7 +2507,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B79" t="n">
@@ -2522,7 +2534,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B80" t="n">
@@ -2549,7 +2561,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B81" t="n">
@@ -2576,7 +2588,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B82" t="n">
@@ -2603,7 +2615,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B83" t="n">
@@ -2630,7 +2642,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B84" t="n">
@@ -2657,7 +2669,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B85" t="n">
@@ -2684,7 +2696,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B86" t="n">
@@ -2709,7 +2721,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B87" t="n">
@@ -2734,7 +2746,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B88" t="n">
@@ -2759,7 +2771,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B89" t="n">
@@ -2784,7 +2796,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B90" t="n">
@@ -2809,7 +2821,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B91" t="n">
@@ -2834,7 +2846,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B92" t="n">
@@ -2859,7 +2871,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B93" t="n">
@@ -2884,7 +2896,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B94" t="n">
@@ -2911,7 +2923,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B95" t="n">
@@ -2938,7 +2950,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B96" t="n">
@@ -2965,7 +2977,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B97" t="n">
@@ -2992,7 +3004,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B98" t="n">
@@ -3019,7 +3031,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B99" t="n">
@@ -3048,7 +3060,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B100" t="n">
@@ -3077,7 +3089,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B101" t="n">
@@ -3106,7 +3118,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B102" t="n">
@@ -3135,7 +3147,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B103" t="n">
@@ -3164,7 +3176,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B104" t="n">
@@ -3193,7 +3205,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B105" t="n">
@@ -3222,7 +3234,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B106" t="n">
@@ -3251,7 +3263,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B107" t="n">
@@ -3280,7 +3292,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B108" t="n">
@@ -3309,7 +3321,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B109" t="n">
@@ -3338,7 +3350,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B110" t="n">
@@ -3367,7 +3379,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B111" t="n">
@@ -3396,7 +3408,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B112" t="n">
@@ -3425,7 +3437,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B113" t="n">
@@ -3454,7 +3466,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B114" t="n">
@@ -3483,7 +3495,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B115" t="n">
@@ -3512,7 +3524,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B116" t="n">
@@ -3541,7 +3553,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B117" t="n">
@@ -3570,7 +3582,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B118" t="n">
@@ -3599,7 +3611,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B119" t="n">
@@ -3628,7 +3640,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B120" t="n">
@@ -3657,7 +3669,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B121" t="n">
@@ -3686,7 +3698,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B122" t="n">
@@ -3715,7 +3727,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B123" t="n">
@@ -3744,7 +3756,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B124" t="n">
@@ -3773,7 +3785,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B125" t="n">
@@ -3802,7 +3814,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B126" t="n">
@@ -3831,7 +3843,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B127" t="n">
@@ -3860,7 +3872,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B128" t="n">
@@ -3889,7 +3901,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B129" t="n">
@@ -3918,7 +3930,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B130" t="n">
@@ -3947,7 +3959,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B131" t="n">
@@ -3976,7 +3988,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B132" t="n">
@@ -4005,7 +4017,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B133" t="n">
@@ -4034,7 +4046,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B134" t="n">
@@ -4063,7 +4075,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B135" t="n">
@@ -4092,7 +4104,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B136" t="n">
@@ -4121,7 +4133,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B137" t="n">
@@ -4150,7 +4162,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B138" t="n">
@@ -4179,7 +4191,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B139" t="n">
@@ -4208,7 +4220,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B140" t="n">
@@ -4237,7 +4249,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B141" t="n">
@@ -4266,7 +4278,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B142" t="n">
@@ -4295,7 +4307,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B143" t="n">
@@ -4324,7 +4336,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B144" t="n">
@@ -4353,7 +4365,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B145" t="n">
@@ -4382,7 +4394,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B146" t="n">
@@ -4411,7 +4423,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B147" t="n">
@@ -4440,7 +4452,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B148" t="n">
@@ -4469,7 +4481,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B149" t="n">
@@ -4498,7 +4510,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B150" t="n">
@@ -4527,7 +4539,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B151" t="n">
@@ -4556,7 +4568,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B152" t="n">
@@ -4585,7 +4597,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B153" t="n">
@@ -4614,7 +4626,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B154" t="n">
@@ -4643,7 +4655,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B155" t="n">
@@ -4672,7 +4684,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B156" t="n">
@@ -4701,7 +4713,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B157" t="n">
@@ -4730,7 +4742,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B158" t="n">
@@ -4759,7 +4771,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B159" t="n">
@@ -4788,7 +4800,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B160" t="n">
@@ -4817,7 +4829,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B161" t="n">
@@ -4846,7 +4858,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B162" t="n">
@@ -4875,7 +4887,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B163" t="n">
@@ -4904,7 +4916,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B164" t="n">
@@ -4933,7 +4945,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B165" t="n">
@@ -4962,7 +4974,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B166" t="n">
@@ -4991,7 +5003,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B167" t="n">
@@ -5020,7 +5032,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B168" t="n">
@@ -5049,7 +5061,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B169" t="n">
@@ -5078,7 +5090,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B170" t="n">
@@ -5107,7 +5119,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B171" t="n">
@@ -5136,7 +5148,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B172" t="n">
@@ -5165,32 +5177,32 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B173" t="n">
-        <v>140.7799987792969</v>
+        <v>137.7799987792969</v>
       </c>
       <c r="C173" t="n">
-        <v>140.7799987792969</v>
+        <v>137.7799987792969</v>
       </c>
       <c r="D173" t="n">
-        <v>218085000</v>
+        <v>227670400</v>
       </c>
       <c r="E173" t="n">
         <v>1.602</v>
       </c>
       <c r="F173" t="n">
-        <v>87.87765217184575</v>
+        <v>86.00499299581578</v>
       </c>
       <c r="G173" t="n">
         <v>1034000000</v>
       </c>
       <c r="H173" t="n">
-        <v>145566518737.793</v>
+        <v>142464518737.793</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2109139264990329</v>
+        <v>0.2201841392649903</v>
       </c>
     </row>
   </sheetData>
@@ -5222,75 +5234,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>41131</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5326,13 +5338,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5368,13 +5380,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5410,13 +5422,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41131</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5452,13 +5464,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -5494,13 +5506,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -5536,13 +5548,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -5578,13 +5590,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -5620,13 +5632,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -5653,7 +5665,7 @@
       <c r="I10" t="n">
         <v>-0.108</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K10" t="n">
@@ -5666,13 +5678,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -5699,7 +5711,7 @@
       <c r="I11" t="n">
         <v>-0.148</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K11" t="n">
@@ -5712,13 +5724,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -5745,7 +5757,7 @@
       <c r="I12" t="n">
         <v>-0.186</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="K12" t="n">
@@ -5758,13 +5770,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -5791,7 +5803,7 @@
       <c r="I13" t="n">
         <v>-0.22</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K13" t="n">
@@ -5804,13 +5816,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -5837,7 +5849,7 @@
       <c r="I14" t="n">
         <v>-0.246</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K14" t="n">
@@ -5850,13 +5862,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -5883,7 +5895,7 @@
       <c r="I15" t="n">
         <v>-0.262</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K15" t="n">
@@ -5896,13 +5908,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -5929,7 +5941,7 @@
       <c r="I16" t="n">
         <v>-0.272</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K16" t="n">
@@ -5942,13 +5954,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -5975,7 +5987,7 @@
       <c r="I17" t="n">
         <v>-0.268</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K17" t="n">
@@ -5988,13 +6000,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6021,7 +6033,7 @@
       <c r="I18" t="n">
         <v>-0.254</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K18" t="n">
@@ -6034,13 +6046,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6067,7 +6079,7 @@
       <c r="I19" t="n">
         <v>-0.5900000000000001</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K19" t="n">
@@ -6080,13 +6092,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6113,7 +6125,7 @@
       <c r="I20" t="n">
         <v>-0.5700000000000001</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K20" t="n">
@@ -6126,13 +6138,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6159,7 +6171,7 @@
       <c r="I21" t="n">
         <v>-0.5620000000000001</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K21" t="n">
@@ -6172,13 +6184,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6205,7 +6217,7 @@
       <c r="I22" t="n">
         <v>-0.55</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="K22" t="n">
@@ -6218,13 +6230,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6251,7 +6263,7 @@
       <c r="I23" t="n">
         <v>-0.164</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="K23" t="n">
@@ -6264,13 +6276,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6297,7 +6309,7 @@
       <c r="I24" t="n">
         <v>-0.17</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="K24" t="n">
@@ -6310,13 +6322,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6343,7 +6355,7 @@
       <c r="I25" t="n">
         <v>-0.1520000000000001</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K25" t="n">
@@ -6356,13 +6368,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6389,7 +6401,7 @@
       <c r="I26" t="n">
         <v>-0.15</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K26" t="n">
@@ -6402,13 +6414,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -6435,7 +6447,7 @@
       <c r="I27" t="n">
         <v>-0.112</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K27" t="n">
@@ -6448,13 +6460,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -6481,7 +6493,7 @@
       <c r="I28" t="n">
         <v>-0.106</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K28" t="n">
@@ -6494,13 +6506,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -6527,7 +6539,7 @@
       <c r="I29" t="n">
         <v>-0.07199999999999998</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K29" t="n">
@@ -6540,13 +6552,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -6573,7 +6585,7 @@
       <c r="I30" t="n">
         <v>-0.03000000000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K30" t="n">
@@ -6586,13 +6598,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -6619,7 +6631,7 @@
       <c r="I31" t="n">
         <v>-0.04400000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K31" t="n">
@@ -6632,13 +6644,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -6665,7 +6677,7 @@
       <c r="I32" t="n">
         <v>0.003999999999999988</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K32" t="n">
@@ -6678,13 +6690,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -6711,7 +6723,7 @@
       <c r="I33" t="n">
         <v>0.03799999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K33" t="n">
@@ -6724,13 +6736,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -6757,7 +6769,7 @@
       <c r="I34" t="n">
         <v>0.6351543379828924</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K34" t="n">
@@ -6770,13 +6782,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -6803,7 +6815,7 @@
       <c r="I35" t="n">
         <v>0.6851543379828925</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K35" t="n">
@@ -6816,13 +6828,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -6849,7 +6861,7 @@
       <c r="I36" t="n">
         <v>0.7371543379828924</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K36" t="n">
@@ -6862,13 +6874,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -6895,7 +6907,7 @@
       <c r="I37" t="n">
         <v>0.7071543379828924</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K37" t="n">
@@ -6908,13 +6920,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -6941,7 +6953,7 @@
       <c r="I38" t="n">
         <v>0.118</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="K38" t="n">
@@ -6954,13 +6966,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -6987,7 +6999,7 @@
       <c r="I39" t="n">
         <v>0.152</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K39" t="n">
@@ -7000,13 +7012,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7033,7 +7045,7 @@
       <c r="I40" t="n">
         <v>0.17</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K40" t="n">
@@ -7046,13 +7058,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7079,7 +7091,7 @@
       <c r="I41" t="n">
         <v>0.22</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K41" t="n">
@@ -7092,13 +7104,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7125,7 +7137,7 @@
       <c r="I42" t="n">
         <v>0.226</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="K42" t="n">
@@ -7138,13 +7150,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7171,7 +7183,7 @@
       <c r="I43" t="n">
         <v>0.218</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K43" t="n">
@@ -7184,13 +7196,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7217,7 +7229,7 @@
       <c r="I44" t="n">
         <v>0.18</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K44" t="n">
@@ -7230,13 +7242,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -7263,7 +7275,7 @@
       <c r="I45" t="n">
         <v>0.196</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K45" t="n">
@@ -7276,13 +7288,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -7309,7 +7321,7 @@
       <c r="I46" t="n">
         <v>0.3200000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="K46" t="n">
@@ -7322,13 +7334,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -7355,7 +7367,7 @@
       <c r="I47" t="n">
         <v>0.392</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K47" t="n">
@@ -7368,13 +7380,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -7401,7 +7413,7 @@
       <c r="I48" t="n">
         <v>1.388</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K48" t="n">
@@ -7414,13 +7426,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -7447,7 +7459,7 @@
       <c r="I49" t="n">
         <v>1.544</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K49" t="n">
@@ -7460,13 +7472,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45316</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -7493,7 +7505,7 @@
       <c r="I50" t="n">
         <v>1.684</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45316</v>
       </c>
       <c r="K50" t="n">
@@ -7506,13 +7518,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -7539,7 +7551,7 @@
       <c r="I51" t="n">
         <v>1.872</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="K51" t="n">
@@ -7552,13 +7564,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -7585,7 +7597,7 @@
       <c r="I52" t="n">
         <v>1.108</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K52" t="n">
@@ -7598,13 +7610,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -7631,7 +7643,7 @@
       <c r="I53" t="n">
         <v>1.288</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="K53" t="n">
@@ -7644,13 +7656,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -7677,7 +7689,7 @@
       <c r="I54" t="n">
         <v>1.368</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="K54" t="n">
@@ -7690,13 +7702,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -7723,7 +7735,7 @@
       <c r="I55" t="n">
         <v>1.474</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K55" t="n">
@@ -7736,13 +7748,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -7769,7 +7781,7 @@
       <c r="I56" t="n">
         <v>1.59</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K56" t="n">
@@ -7782,13 +7794,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -7815,7 +7827,7 @@
       <c r="I57" t="n">
         <v>1.656</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K57" t="n">
@@ -7828,13 +7840,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -7861,7 +7873,7 @@
       <c r="I58" t="n">
         <v>1.67</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="K58" t="n">
@@ -7874,13 +7886,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -7907,7 +7919,7 @@
       <c r="I59" t="n">
         <v>1.68</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="K59" t="n">
@@ -7920,13 +7932,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -7953,7 +7965,7 @@
       <c r="I60" t="n">
         <v>1.602</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="K60" t="n">
@@ -7990,52 +8002,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41127</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41131</v>
       </c>
       <c r="C2" t="n">
@@ -8064,10 +8076,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41207</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="C3" t="n">
@@ -8096,10 +8108,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41341</v>
       </c>
       <c r="C4" t="n">
@@ -8128,10 +8140,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C5" t="n">
@@ -8160,10 +8172,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C6" t="n">
@@ -8192,10 +8204,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="C7" t="n">
@@ -8224,10 +8236,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C8" t="n">
@@ -8256,10 +8268,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C9" t="n">
@@ -8288,10 +8300,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="C10" t="n">
@@ -8320,10 +8332,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C11" t="n">
@@ -8352,10 +8364,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C12" t="n">
@@ -8384,10 +8396,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C13" t="n">
@@ -8416,10 +8428,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C14" t="n">
@@ -8448,10 +8460,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C15" t="n">
@@ -8480,10 +8492,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C16" t="n">
@@ -8512,10 +8524,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C17" t="n">
@@ -8544,10 +8556,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C18" t="n">
@@ -8576,10 +8588,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C19" t="n">
@@ -8608,10 +8620,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="C20" t="n">
@@ -8640,10 +8652,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C21" t="n">
@@ -8672,10 +8684,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="C22" t="n">
@@ -8704,10 +8716,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43045</v>
       </c>
       <c r="C23" t="n">
@@ -8736,10 +8748,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C24" t="n">
@@ -8768,10 +8780,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="C25" t="n">
@@ -8800,10 +8812,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="C26" t="n">
@@ -8832,10 +8844,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="C27" t="n">
@@ -8864,10 +8876,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="C28" t="n">
@@ -8896,10 +8908,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C29" t="n">
@@ -8928,10 +8940,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C30" t="n">
@@ -8960,10 +8972,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C31" t="n">
@@ -8992,10 +9004,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C32" t="n">
@@ -9024,10 +9036,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C33" t="n">
@@ -9056,10 +9068,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C34" t="n">
@@ -9088,10 +9100,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C35" t="n">
@@ -9120,10 +9132,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="C36" t="n">
@@ -9152,10 +9164,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C37" t="n">
@@ -9184,10 +9196,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C38" t="n">
@@ -9216,10 +9228,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C39" t="n">
@@ -9248,10 +9260,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="C40" t="n">
@@ -9280,10 +9292,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C41" t="n">
@@ -9312,10 +9324,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C42" t="n">
@@ -9344,10 +9356,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C43" t="n">
@@ -9376,10 +9388,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44951</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="C44" t="n">
@@ -9408,10 +9420,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C45" t="n">
@@ -9440,10 +9452,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C46" t="n">
@@ -9472,10 +9484,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C47" t="n">
@@ -9504,10 +9516,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45310</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45316</v>
       </c>
       <c r="C48" t="n">
@@ -9536,10 +9548,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="C49" t="n">
@@ -9568,10 +9580,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C50" t="n">
@@ -9600,10 +9612,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="C51" t="n">
@@ -9632,10 +9644,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45680</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="C52" t="n">
@@ -9664,10 +9676,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="C53" t="n">
@@ -9696,10 +9708,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C54" t="n">
@@ -9728,10 +9740,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C55" t="n">
@@ -9760,10 +9772,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46045</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="C56" t="n">
@@ -9792,10 +9804,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="C57" t="n">
@@ -9824,10 +9836,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="C58" t="n">
@@ -9874,12 +9886,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
